--- a/content/tz-vk/tz-vk-semya-i-rodstvenniki-po-kitajski.xlsx
+++ b/content/tz-vk/tz-vk-semya-i-rodstvenniki-po-kitajski.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -593,25 +593,37 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="33" customHeight="1">
+    <row r="9" ht="63" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
+          <t>Картинки</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>ОБЯЗАТЕЛЬНО: обложка + 1 инфографика. Где нужно — несколько картинок. Мотив обложки: иероглиф 家 «дом/семья». Инфографики: Карточки родственников. Подробно — лист «8. Картинки и проверка».</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="33" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
           <t>Отстройка</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>Через семью показываем культуру: 团圆 и иерархию; даём рабочий минимум родственных слов.</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>Объём</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>3 000–4 500 знаков + карточки</t>
         </is>
@@ -755,7 +767,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -820,34 +832,46 @@
     <row r="6" ht="33" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
+          <t>Инфографики</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>ОБЯЗАТЕЛЬНО 1 шт. (где нужно — несколько): Карточки родственников: 妈妈 爸爸 哥哥 姐姐 弟弟 妹妹 + разбор 家.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="33" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
           <t>Хэштеги</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>#китай #китайскийязык #семьяпокитайски #家 #родственники #учимкитайский #中文</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Формат публикации</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>Карточки-галерея.</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="33" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
+    <row r="9" ht="33" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Ссылки / CTA</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Верх воронки (ст. 0–1) — без офферов. Мягкая ссылка на школу допустима у ст. 2–4, в конце, ненавязчиво.</t>
         </is>
